--- a/data/trans_orig/P1408-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1408-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2007</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16452</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36684</t>
+          <t>34993</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>7913</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>23735</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>26231</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51015</t>
+          <t>51241</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>657328</t>
+          <t>659019</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>677560</t>
+          <t>679074</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>663821</t>
+          <t>664616</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>680136</t>
+          <t>680438</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1331348</t>
+          <t>1331122</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1355131</t>
+          <t>1356132</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36730</t>
+          <t>36108</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66607</t>
+          <t>63780</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16386</t>
+          <t>15958</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>36822</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59589</t>
+          <t>59550</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94719</t>
+          <t>94576</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>895193</t>
+          <t>898020</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>925070</t>
+          <t>925692</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>929806</t>
+          <t>931571</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>952007</t>
+          <t>952435</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1835474</t>
+          <t>1835617</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1870604</t>
+          <t>1870643</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>15368</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36566</t>
+          <t>35613</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31590</t>
+          <t>30421</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33247</t>
+          <t>33456</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58864</t>
+          <t>59138</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>641943</t>
+          <t>642896</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662688</t>
+          <t>663141</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>652251</t>
+          <t>653420</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>670122</t>
+          <t>670605</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1303486</t>
+          <t>1303212</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1329103</t>
+          <t>1328894</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27481</t>
+          <t>27401</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50962</t>
+          <t>50656</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>21530</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42789</t>
+          <t>43464</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54324</t>
+          <t>54662</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86468</t>
+          <t>87086</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>891260</t>
+          <t>891566</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>914741</t>
+          <t>914821</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>995823</t>
+          <t>995148</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1018561</t>
+          <t>1017082</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1894366</t>
+          <t>1893748</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1926510</t>
+          <t>1926172</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115329</t>
+          <t>113437</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>158816</t>
+          <t>157978</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74983</t>
+          <t>73793</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111032</t>
+          <t>112672</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>200369</t>
+          <t>198466</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>258465</t>
+          <t>259841</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3117727</t>
+          <t>3118565</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3161214</t>
+          <t>3163106</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3268165</t>
+          <t>3266525</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3304214</t>
+          <t>3305404</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6397276</t>
+          <t>6395900</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6455372</t>
+          <t>6457275</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2012</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14537</t>
+          <t>14894</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37769</t>
+          <t>37037</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21633</t>
+          <t>21989</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25742</t>
+          <t>26487</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53166</t>
+          <t>53176</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>665700</t>
+          <t>666432</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>688932</t>
+          <t>688575</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>675417</t>
+          <t>675061</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>690679</t>
+          <t>690907</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1347353</t>
+          <t>1347343</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1374777</t>
+          <t>1374032</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11991</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30301</t>
+          <t>30944</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16642</t>
+          <t>17970</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>19593</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41410</t>
+          <t>41569</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>987646</t>
+          <t>987003</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1005956</t>
+          <t>1005845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1011149</t>
+          <t>1009821</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1023524</t>
+          <t>1022617</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2004328</t>
+          <t>2004169</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2026039</t>
+          <t>2026145</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>8182</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25857</t>
+          <t>25848</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13927</t>
+          <t>14117</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13629</t>
+          <t>13599</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34305</t>
+          <t>33247</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>731766</t>
+          <t>731775</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>749259</t>
+          <t>749441</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>763247</t>
+          <t>763057</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>774021</t>
+          <t>774034</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1500492</t>
+          <t>1501550</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1521168</t>
+          <t>1521198</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8867</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24167</t>
+          <t>23669</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22059</t>
+          <t>21281</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19972</t>
+          <t>19109</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40584</t>
+          <t>40079</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>923572</t>
+          <t>924070</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>938872</t>
+          <t>939552</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1029842</t>
+          <t>1030620</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1044830</t>
+          <t>1044369</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1959056</t>
+          <t>1959561</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1979668</t>
+          <t>1980531</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58749</t>
+          <t>56944</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96904</t>
+          <t>93437</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>31756</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58750</t>
+          <t>58506</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94290</t>
+          <t>95569</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>140732</t>
+          <t>139176</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3329875</t>
+          <t>3333342</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3368030</t>
+          <t>3369835</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3495166</t>
+          <t>3495410</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3523007</t>
+          <t>3522160</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6839962</t>
+          <t>6841518</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6886404</t>
+          <t>6885125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2016</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17632</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4337</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>17456</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>11561</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29825</t>
+          <t>29679</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>657168</t>
+          <t>657539</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>670048</t>
+          <t>669786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>655839</t>
+          <t>655383</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>668666</t>
+          <t>668502</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1317814</t>
+          <t>1317960</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1336336</t>
+          <t>1336078</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14130</t>
+          <t>13752</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32236</t>
+          <t>33089</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>8377</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24197</t>
+          <t>25058</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26073</t>
+          <t>25291</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50130</t>
+          <t>50245</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>990195</t>
+          <t>989342</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1008301</t>
+          <t>1008679</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1018716</t>
+          <t>1017855</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1035237</t>
+          <t>1034536</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2015214</t>
+          <t>2015099</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2039271</t>
+          <t>2040053</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22360</t>
+          <t>21602</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24459</t>
+          <t>24591</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17212</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>39332</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>737192</t>
+          <t>737950</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>752655</t>
+          <t>753075</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>760552</t>
+          <t>760420</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>777531</t>
+          <t>777561</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1505666</t>
+          <t>1505231</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1527351</t>
+          <t>1527205</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14702</t>
+          <t>14875</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33463</t>
+          <t>33311</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16185</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21836</t>
+          <t>20983</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41913</t>
+          <t>42343</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>904104</t>
+          <t>904256</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>922865</t>
+          <t>922692</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1027594</t>
+          <t>1028082</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1040436</t>
+          <t>1040443</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1939433</t>
+          <t>1939003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1959510</t>
+          <t>1960363</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51511</t>
+          <t>51201</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85453</t>
+          <t>83469</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32981</t>
+          <t>33464</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61614</t>
+          <t>60705</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92245</t>
+          <t>91677</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135720</t>
+          <t>132478</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3308897</t>
+          <t>3310881</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3342839</t>
+          <t>3343149</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3482928</t>
+          <t>3483837</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3511561</t>
+          <t>3511078</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6803172</t>
+          <t>6806414</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6846647</t>
+          <t>6847215</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2023</t>
+          <t>Población con diagnóstico de enfermedad crónica de pulmón en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15073</t>
+          <t>14328</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30509</t>
+          <t>30277</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13680</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25616</t>
+          <t>25887</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31449</t>
+          <t>29694</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50930</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>604932</t>
+          <t>605164</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>620368</t>
+          <t>621113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>649235</t>
+          <t>648964</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>661171</t>
+          <t>661087</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1259362</t>
+          <t>1260380</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1278843</t>
+          <t>1280598</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>11854</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34162</t>
+          <t>34356</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18145</t>
+          <t>17711</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37765</t>
+          <t>38082</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31176</t>
+          <t>30903</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62265</t>
+          <t>62478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1158702</t>
+          <t>1158508</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1182141</t>
+          <t>1181010</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>919145</t>
+          <t>918828</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>938765</t>
+          <t>939199</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2087509</t>
+          <t>2087296</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2118598</t>
+          <t>2118871</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10228</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26649</t>
+          <t>25750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>5627</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25572</t>
+          <t>23955</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18543</t>
+          <t>19309</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44565</t>
+          <t>44378</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>676316</t>
+          <t>677215</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>692737</t>
+          <t>692435</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>905625</t>
+          <t>907242</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>924597</t>
+          <t>925570</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1589596</t>
+          <t>1589783</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1615618</t>
+          <t>1614852</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15707</t>
+          <t>16068</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32455</t>
+          <t>31402</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22172</t>
+          <t>21913</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41571</t>
+          <t>42680</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41951</t>
+          <t>42421</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67723</t>
+          <t>68971</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>893300</t>
+          <t>894353</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>910048</t>
+          <t>909687</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1049945</t>
+          <t>1048836</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1069344</t>
+          <t>1069603</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1949548</t>
+          <t>1948300</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1975320</t>
+          <t>1974850</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63471</t>
+          <t>62876</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102715</t>
+          <t>101720</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,82 +7961,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>88570</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>70208</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>108383</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
           <t>2,97%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>88570</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>71014</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>107790</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>172262</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>144396</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>201656</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>2,42%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>172262</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>147277</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>200879</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3354311</t>
+          <t>3355306</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3393555</t>
+          <t>3394150</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,82 +8074,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>97,06%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5198</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3565904</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3546091</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3584266</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>97,03%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,16%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5198</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3565904</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3546684</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3583460</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>98,08%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>8454</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>6939237</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>6909843</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6967103</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>97,58%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>98,06%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>8454</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6939237</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6910620</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6964222</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1408-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1408-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14938</t>
+          <t>15663</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34993</t>
+          <t>34681</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23735</t>
+          <t>22722</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26231</t>
+          <t>27729</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51241</t>
+          <t>51455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>659019</t>
+          <t>659331</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>679074</t>
+          <t>678349</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>664616</t>
+          <t>665629</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>680438</t>
+          <t>680409</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1331122</t>
+          <t>1330908</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1356132</t>
+          <t>1354634</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36108</t>
+          <t>35588</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63780</t>
+          <t>65243</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15958</t>
+          <t>16321</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36822</t>
+          <t>38564</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59550</t>
+          <t>59171</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94576</t>
+          <t>92607</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>898020</t>
+          <t>896557</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>925692</t>
+          <t>926212</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>931571</t>
+          <t>929829</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>952435</t>
+          <t>952072</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1835617</t>
+          <t>1837586</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1870643</t>
+          <t>1871022</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15368</t>
+          <t>15318</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35613</t>
+          <t>34718</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13236</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30421</t>
+          <t>32382</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33456</t>
+          <t>34066</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59138</t>
+          <t>59612</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>642896</t>
+          <t>643791</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663141</t>
+          <t>663191</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>653420</t>
+          <t>651459</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>670605</t>
+          <t>669799</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1303212</t>
+          <t>1302738</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1328894</t>
+          <t>1328284</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27401</t>
+          <t>28888</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50656</t>
+          <t>52027</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>20263</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43464</t>
+          <t>41846</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54662</t>
+          <t>54633</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87086</t>
+          <t>86818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>891566</t>
+          <t>890195</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>914821</t>
+          <t>913334</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>995148</t>
+          <t>996766</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1017082</t>
+          <t>1018349</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1893748</t>
+          <t>1894016</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1926172</t>
+          <t>1926201</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>113437</t>
+          <t>116127</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>157978</t>
+          <t>161980</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73793</t>
+          <t>74356</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>112672</t>
+          <t>110814</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>198466</t>
+          <t>199435</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>259841</t>
+          <t>257911</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3118565</t>
+          <t>3114563</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3163106</t>
+          <t>3160416</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3266525</t>
+          <t>3268383</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3305404</t>
+          <t>3304841</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6395900</t>
+          <t>6397830</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6457275</t>
+          <t>6456306</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14894</t>
+          <t>14949</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37037</t>
+          <t>38325</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21989</t>
+          <t>21225</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26487</t>
+          <t>24837</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53176</t>
+          <t>50541</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>666432</t>
+          <t>665144</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>688575</t>
+          <t>688520</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>675061</t>
+          <t>675825</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>690907</t>
+          <t>690610</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1347343</t>
+          <t>1349978</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1374032</t>
+          <t>1375682</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12102</t>
+          <t>12130</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30944</t>
+          <t>30595</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17970</t>
+          <t>17668</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19593</t>
+          <t>19822</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41569</t>
+          <t>42172</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>987003</t>
+          <t>987352</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1005845</t>
+          <t>1005817</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1009821</t>
+          <t>1010123</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1022617</t>
+          <t>1022684</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2004169</t>
+          <t>2003566</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2026145</t>
+          <t>2025916</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25848</t>
+          <t>25214</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14117</t>
+          <t>14895</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13599</t>
+          <t>13586</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33247</t>
+          <t>32863</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>731775</t>
+          <t>732409</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>749441</t>
+          <t>749528</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>763057</t>
+          <t>762279</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>774034</t>
+          <t>773994</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1501550</t>
+          <t>1501934</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1521198</t>
+          <t>1521211</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8187</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23669</t>
+          <t>25320</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21281</t>
+          <t>22228</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19109</t>
+          <t>19130</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40079</t>
+          <t>40160</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>924070</t>
+          <t>922419</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>939552</t>
+          <t>938663</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1030620</t>
+          <t>1029673</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1044369</t>
+          <t>1043892</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1959561</t>
+          <t>1959480</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1980531</t>
+          <t>1980510</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56944</t>
+          <t>55218</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93437</t>
+          <t>91308</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,74 +4067,74 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>42468</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>30856</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>57667</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>116121</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>95606</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>141689</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>1,66%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>42468</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>31756</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>58506</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>116121</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>95569</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>139176</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
           <t>1,37%</t>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3333342</t>
+          <t>3335471</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3369835</t>
+          <t>3371561</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,77 +4180,77 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3511448</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3496249</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3523060</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>98,81%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>6398</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>6864573</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>6839005</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6885088</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>98,34%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3255</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3511448</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3495410</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3522160</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>6398</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6864573</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6841518</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6885125</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>17303</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17456</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29679</t>
+          <t>29233</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>657539</t>
+          <t>657497</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>669786</t>
+          <t>669963</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>655383</t>
+          <t>655905</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>668502</t>
+          <t>668565</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1317960</t>
+          <t>1318406</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1336078</t>
+          <t>1335499</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13752</t>
+          <t>13955</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33089</t>
+          <t>33016</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25058</t>
+          <t>24599</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25291</t>
+          <t>24920</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50245</t>
+          <t>50193</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>989342</t>
+          <t>989415</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1008679</t>
+          <t>1008476</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1017855</t>
+          <t>1018314</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1034536</t>
+          <t>1035080</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2015099</t>
+          <t>2015151</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2040053</t>
+          <t>2040424</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>6474</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21602</t>
+          <t>22157</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24591</t>
+          <t>23225</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>16818</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39332</t>
+          <t>38453</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>737950</t>
+          <t>737395</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>753075</t>
+          <t>753078</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>760420</t>
+          <t>761786</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>777561</t>
+          <t>777784</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1505231</t>
+          <t>1506110</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1527205</t>
+          <t>1527745</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33311</t>
+          <t>33269</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15697</t>
+          <t>15026</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20983</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42343</t>
+          <t>43701</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>904256</t>
+          <t>904298</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>922692</t>
+          <t>922610</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1028082</t>
+          <t>1028753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1040443</t>
+          <t>1040498</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1939003</t>
+          <t>1937645</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1960363</t>
+          <t>1960476</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51201</t>
+          <t>51915</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83469</t>
+          <t>84355</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33464</t>
+          <t>31237</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60705</t>
+          <t>60482</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91677</t>
+          <t>92622</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>132478</t>
+          <t>132714</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3310881</t>
+          <t>3309995</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3343149</t>
+          <t>3342435</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3483837</t>
+          <t>3484060</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3511078</t>
+          <t>3513305</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6806414</t>
+          <t>6806178</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6847215</t>
+          <t>6846270</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -6569,102 +6569,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21127</t>
+          <t>21978</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14328</t>
+          <t>15123</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30277</t>
+          <t>32385</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>19679</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>13981</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>26756</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>41658</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>32055</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>52926</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>2,25%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>18911</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>13764</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>25887</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>40038</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>29694</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>49912</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -6682,102 +6682,102 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>614314</t>
+          <t>668732</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>605164</t>
+          <t>658325</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>621113</t>
+          <t>675587</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1196</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>712508</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>705431</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>718206</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>97,31%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,35%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>98,09%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1894</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1381239</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1369971</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1390842</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>97,07%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>96,28%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>97,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1196</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>655940</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>648964</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>661087</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,16%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>97,96%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1894</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1270254</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1260380</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1280598</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,94%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>96,19%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674851</t>
+          <t>732187</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674851</t>
+          <t>732187</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674851</t>
+          <t>732187</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310292</t>
+          <t>1422897</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310292</t>
+          <t>1422897</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310292</t>
+          <t>1422897</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22826</t>
+          <t>24242</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11854</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34356</t>
+          <t>34406</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24605</t>
+          <t>27160</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17711</t>
+          <t>19095</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38082</t>
+          <t>41255</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>47431</t>
+          <t>51402</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30903</t>
+          <t>39682</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62478</t>
+          <t>69376</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1170038</t>
+          <t>1024675</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1158508</t>
+          <t>1014511</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1181010</t>
+          <t>1032250</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>932305</t>
+          <t>1042458</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>918828</t>
+          <t>1028363</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>939199</t>
+          <t>1050523</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2102343</t>
+          <t>2067133</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2087296</t>
+          <t>2049159</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2118871</t>
+          <t>2078853</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>956910</t>
+          <t>1069618</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>956910</t>
+          <t>1069618</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>956910</t>
+          <t>1069618</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2149774</t>
+          <t>2118535</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2149774</t>
+          <t>2118535</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2149774</t>
+          <t>2118535</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,102 +7255,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16661</t>
+          <t>17957</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10530</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25750</t>
+          <t>28835</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>15391</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9615</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>24616</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>33348</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>24159</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>45806</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>1,5%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>14052</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5627</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>23955</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>30713</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>19309</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>44378</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -7368,102 +7368,102 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>686304</t>
+          <t>783260</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>677215</t>
+          <t>772382</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>692435</t>
+          <t>789789</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>98,57%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>793468</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>784243</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>799244</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,1%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>98,81%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1677</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1576728</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1564270</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1585917</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>97,93%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>97,16%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>98,5%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1022</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>917145</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>907242</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>925570</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,49%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1677</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1603448</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1589783</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1614852</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>98,12%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>97,28%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>931197</t>
+          <t>808859</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>931197</t>
+          <t>808859</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>931197</t>
+          <t>808859</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1634161</t>
+          <t>1610076</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1634161</t>
+          <t>1610076</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1634161</t>
+          <t>1610076</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23078</t>
+          <t>25818</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16068</t>
+          <t>18291</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31402</t>
+          <t>36428</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31002</t>
+          <t>33590</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21913</t>
+          <t>24832</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42680</t>
+          <t>45051</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>54080</t>
+          <t>59408</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42421</t>
+          <t>47849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68971</t>
+          <t>74186</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>902677</t>
+          <t>963146</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>894353</t>
+          <t>952536</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>909687</t>
+          <t>970673</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1060514</t>
+          <t>1083643</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1048836</t>
+          <t>1072182</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1069603</t>
+          <t>1092401</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1963191</t>
+          <t>2046790</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1948300</t>
+          <t>2032012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1974850</t>
+          <t>2058349</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>925755</t>
+          <t>988964</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>925755</t>
+          <t>988964</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>925755</t>
+          <t>988964</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091516</t>
+          <t>1117233</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091516</t>
+          <t>1117233</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091516</t>
+          <t>1117233</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2017271</t>
+          <t>2106198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2017271</t>
+          <t>2106198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2017271</t>
+          <t>2106198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>83692</t>
+          <t>89995</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62876</t>
+          <t>72487</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101720</t>
+          <t>107672</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>88570</t>
+          <t>95820</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70208</t>
+          <t>81023</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108383</t>
+          <t>113973</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>172262</t>
+          <t>185815</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>144396</t>
+          <t>159961</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>201656</t>
+          <t>211854</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3373334</t>
+          <t>3439813</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3355306</t>
+          <t>3422136</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3394150</t>
+          <t>3457321</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3565904</t>
+          <t>3632077</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3546091</t>
+          <t>3613924</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3584266</t>
+          <t>3646874</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6939237</t>
+          <t>7071891</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6909843</t>
+          <t>7045852</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6967103</t>
+          <t>7097745</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3457026</t>
+          <t>3529808</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3457026</t>
+          <t>3529808</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3457026</t>
+          <t>3529808</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3654474</t>
+          <t>3727897</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3654474</t>
+          <t>3727897</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3654474</t>
+          <t>3727897</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7111499</t>
+          <t>7257706</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7111499</t>
+          <t>7257706</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7111499</t>
+          <t>7257706</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
